--- a/Guia_Elicitacion_Yaqui_Catalogo_Completo.xlsx
+++ b/Guia_Elicitacion_Yaqui_Catalogo_Completo.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léxico Yaqui (210)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léxico Yaqui (206)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Léxico Yaqui (210)'!$A$1:$G$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Léxico Yaqui (206)'!$A$1:$G$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,18 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -101,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +127,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -125,9 +143,15 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2712,7 +2736,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -2962,7 +2986,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>112</row>
+      <row>121</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3387,7 +3411,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>138</row>
+      <row>140</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3412,7 +3436,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>139</row>
+      <row>141</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3662,7 +3686,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>151</row>
+      <row>157</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3687,7 +3711,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>152</row>
+      <row>158</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3937,7 +3961,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>168</row>
+      <row>170</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -3962,7 +3986,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>169</row>
+      <row>171</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -4187,7 +4211,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>180</row>
+      <row>194</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -4212,7 +4236,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>181</row>
+      <row>195</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -4237,7 +4261,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>182</row>
+      <row>196</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -4362,7 +4386,7 @@
     <from>
       <col>2</col>
       <colOff>285750</colOff>
-      <row>201</row>
+      <row>203</row>
       <rowOff>85725</rowOff>
     </from>
     <ext cx="438150" cy="438150"/>
@@ -4373,106 +4397,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId167"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>285750</colOff>
-      <row>202</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <ext cx="438150" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="168" name="Image 168" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId168"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>285750</colOff>
-      <row>203</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <ext cx="438150" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="169" name="Image 169" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId169"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>285750</colOff>
-      <row>204</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <ext cx="438150" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="170" name="Image 170" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId170"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>285750</colOff>
-      <row>207</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <ext cx="438150" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="171" name="Image 171" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId171"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4775,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4820,7 +4744,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Notas / Variantes Dialectales</t>
+          <t>Notas / Referencia Fuente</t>
         </is>
       </c>
     </row>
@@ -4839,28 +4763,44 @@
           <t>Águila</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>ba'ajwe</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Ardilla</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>chiku</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 60</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -4877,28 +4817,44 @@
           <t>Borrego</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>kaba</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 87</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Burro</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>buuru</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 54</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -4915,28 +4871,44 @@
           <t>Caballo</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>kaba'i</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 87</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Cerdo</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>kochi</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 94</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -4953,28 +4925,44 @@
           <t>Chivito</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>ili kaba'i</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 03.380</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Conejo</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>taabu</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 141</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -4991,28 +4979,44 @@
           <t>Coyote</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>wo'i</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 159</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Gallina</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>toto'i</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 150</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -5029,28 +5033,44 @@
           <t>Gato</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>miisi</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 107</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Gusano</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bwichia</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 55</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -5067,28 +5087,44 @@
           <t>Hormiga</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>orobwi</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 120</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Lagartija</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>otokoi</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 120</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -5105,28 +5141,44 @@
           <t>Mariposa</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>sebaro'i</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 132</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Mosca</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>sebe</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 132</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -5143,28 +5195,44 @@
           <t>Oso</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>jo'oso</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 03.730</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Perro</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>chu'u</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 62</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -5181,28 +5249,44 @@
           <t>Pez</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>kuchu</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 97</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Pájaro</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>wikit</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 158</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -5219,28 +5303,44 @@
           <t>Rana</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>bwikwe</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 56</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Ratón</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>toori</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 150</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -5257,28 +5357,44 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>bwikoi</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 56</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Serpiente</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>bakot</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 45</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -5295,28 +5411,44 @@
           <t>Vaca</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>wakaj</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 155</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Venado</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>maaso</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 103</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -5333,28 +5465,44 @@
           <t>Zorrillo</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>pisuk</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 125</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Zorro</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>kawis</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 03.740</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -5371,28 +5519,44 @@
           <t>Tortuga</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>mochik</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 107</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Animales</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Pato</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>pato</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 03.570</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -5409,28 +5573,44 @@
           <t>Alacrán</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>tomat</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 149</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Árbol</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>juya</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 85</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -5447,28 +5627,44 @@
           <t>Arcoíris</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>kurues</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 99</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Barranca</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>ba'ara</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -5485,28 +5681,44 @@
           <t>Cueva</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>te'opoi</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Estrella</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>choki</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 60</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -5523,28 +5735,44 @@
           <t>Flor</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>sewa</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 134</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Fuego</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>taji</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 142</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -5561,28 +5789,44 @@
           <t>Hoja</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>saawa</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 131</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Hongo</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>burusiisi</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 08.980</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -5599,28 +5843,44 @@
           <t>Lluvia</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>yuku</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 164</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>Luna</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr"/>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>mecha</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 106</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -5637,28 +5897,44 @@
           <t>Manantial</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>ba'a</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 42</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr"/>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>baawe</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -5675,28 +5951,44 @@
           <t>Monte</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>juya</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 85</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr"/>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr"/>
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Nieve</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr"/>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>sepam</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 01.760</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -5713,28 +6005,44 @@
           <t>Nopal</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>naabo</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 113</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr"/>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr"/>
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Nube</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="6" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr"/>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>namukia</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 114</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -5751,28 +6059,44 @@
           <t>Piedra</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>teta</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 146</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr"/>
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Rama</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr"/>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>maka</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -5789,28 +6113,44 @@
           <t>Raíz</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>naawa</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 113</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr"/>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Río</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr"/>
-      <c r="G53" s="6" t="inlineStr"/>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>batwe</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 47</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -5827,28 +6167,44 @@
           <t>Sol</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>taa'a</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 141</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr"/>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr"/>
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Tierra</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr"/>
-      <c r="G55" s="6" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>bwiya</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 57</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -5865,28 +6221,44 @@
           <t>Trueno</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>tirisia</t>
+        </is>
+      </c>
       <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 148</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Naturaleza</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr"/>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr"/>
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Viento</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr"/>
-      <c r="F57" s="6" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr"/>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>jeecha</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 75</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -5903,28 +6275,44 @@
           <t>Sahuaro</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>aaki</t>
+        </is>
+      </c>
       <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 35</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr"/>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="6" t="inlineStr"/>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>ba'am</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -5941,28 +6329,44 @@
           <t>Atole</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>posorit</t>
+        </is>
+      </c>
       <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 125</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr"/>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Bellota</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr"/>
-      <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr"/>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>beyoota</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 08.660</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -5979,28 +6383,44 @@
           <t>Café</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>kapee</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 90</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr"/>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr"/>
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>Calabaza</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr"/>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>kamocha</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 89</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -6017,28 +6437,44 @@
           <t>Carne</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>wakas</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 155</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Cereza</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr"/>
+      <c r="C65" s="8" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>koko'i</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 95</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -6052,31 +6488,47 @@
       <c r="C66" s="3" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr"/>
+          <t>Frijol</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>munim</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 110</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="48" customHeight="1">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Frijol</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="6" t="inlineStr"/>
+      <c r="C67" s="8" t="inlineStr"/>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Huevo</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>koba</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 94</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -6090,31 +6542,47 @@
       <c r="C68" s="3" t="inlineStr"/>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Huevo</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
+          <t>Leche</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>pweche</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 127</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Leche</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr"/>
+      <c r="C69" s="8" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Manzana</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>mansaana</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -6128,31 +6596,47 @@
       <c r="C70" s="3" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Manzana</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr"/>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>bachi</t>
+        </is>
+      </c>
       <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="3" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="48" customHeight="1">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Maíz</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr"/>
-      <c r="G71" s="6" t="inlineStr"/>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>pan</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 123</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -6166,31 +6650,47 @@
       <c r="C72" s="3" t="inlineStr"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Pan</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr"/>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>paapa</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 122</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Papa</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr"/>
+      <c r="C73" s="8" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Pinole</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>kobisi</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 94</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -6204,31 +6704,47 @@
       <c r="C74" s="3" t="inlineStr"/>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Pinole</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr"/>
+          <t>Quelite</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>baajup</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="48" customHeight="1">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Quelite</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr"/>
-      <c r="F75" s="6" t="inlineStr"/>
-      <c r="G75" s="6" t="inlineStr"/>
+      <c r="C75" s="8" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>ona</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 120</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -6242,31 +6758,47 @@
       <c r="C76" s="3" t="inlineStr"/>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Sal</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr"/>
+          <t>Tesgüino</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>bika yijtela</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 05.940</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="48" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Tesgüino</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr"/>
-      <c r="F77" s="6" t="inlineStr"/>
-      <c r="G77" s="6" t="inlineStr"/>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Tortilla</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>tajkai</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr"/>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 142</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -6280,31 +6812,47 @@
       <c r="C78" s="3" t="inlineStr"/>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Tortilla</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr"/>
+          <t>Trigo</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>tiiko</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 147</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Trigo</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr"/>
-      <c r="F79" s="6" t="inlineStr"/>
-      <c r="G79" s="6" t="inlineStr"/>
+      <c r="C79" s="8" t="inlineStr"/>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Pitahaya</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>aaki</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr"/>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 35</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -6318,31 +6866,47 @@
       <c r="C80" s="3" t="inlineStr"/>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Pitahaya</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr"/>
+          <t>Tamal</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>noka</t>
+        </is>
+      </c>
       <c r="F80" s="3" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 117</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="48" customHeight="1">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Comida y bebida</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Tamal</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr"/>
+      <c r="C81" s="8" t="inlineStr"/>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Caldo</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>wakabaki</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 155</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -6350,37 +6914,53 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Comida y bebida</t>
+          <t>Objetos y hogar</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr"/>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Caldo</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr"/>
+          <t>Bastón</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>boonia</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 52</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="48" customHeight="1">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Bastón</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr"/>
+      <c r="C83" s="8" t="inlineStr"/>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Bolsa</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>kostaal</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr"/>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 97</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -6394,31 +6974,47 @@
       <c r="C84" s="3" t="inlineStr"/>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Bolsa</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr"/>
+          <t>Cama</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>kama</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 89</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Cama</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr"/>
-      <c r="F85" s="6" t="inlineStr"/>
-      <c r="G85" s="6" t="inlineStr"/>
+      <c r="C85" s="8" t="inlineStr"/>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Cesta</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>waja</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 155</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -6432,31 +7028,47 @@
       <c r="C86" s="3" t="inlineStr"/>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Cesta</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr"/>
+          <t>Cobija</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>tajo'ori</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 143</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="48" customHeight="1">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Cobija</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr"/>
-      <c r="F87" s="6" t="inlineStr"/>
-      <c r="G87" s="6" t="inlineStr"/>
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Comal</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>komaal</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 96</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -6470,31 +7082,47 @@
       <c r="C88" s="3" t="inlineStr"/>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Comal</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr"/>
+          <t>Cuchillo</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>kuchim</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 97</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="48" customHeight="1">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Cuchillo</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr"/>
+      <c r="C89" s="8" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Cuerda</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>bwiki</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr"/>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 56</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -6508,31 +7136,47 @@
       <c r="C90" s="3" t="inlineStr"/>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Cuerda</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr"/>
+          <t>Escoba</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>wojta</t>
+        </is>
+      </c>
       <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 159</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="48" customHeight="1">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Escoba</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr"/>
-      <c r="G91" s="6" t="inlineStr"/>
+      <c r="C91" s="8" t="inlineStr"/>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Hacha</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>jecha</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 75</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -6546,31 +7190,47 @@
       <c r="C92" s="3" t="inlineStr"/>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Hacha</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr"/>
+          <t>Jarro</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>soto'i</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 138</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="48" customHeight="1">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Jarro</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr"/>
-      <c r="G93" s="6" t="inlineStr"/>
+      <c r="C93" s="8" t="inlineStr"/>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Leña</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>kuuta</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr"/>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 100</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -6584,31 +7244,47 @@
       <c r="C94" s="3" t="inlineStr"/>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Leña</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr"/>
+          <t>Papel</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>ji'ojte</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 76</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Papel</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="6" t="inlineStr"/>
-      <c r="G95" s="6" t="inlineStr"/>
+      <c r="C95" s="8" t="inlineStr"/>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Pelota</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>pelo'ota</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 124</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -6622,31 +7298,47 @@
       <c r="C96" s="3" t="inlineStr"/>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Pelota</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr"/>
+          <t>Puerta</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>etapo</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 66</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="48" customHeight="1">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Puerta</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr"/>
-      <c r="F97" s="6" t="inlineStr"/>
-      <c r="G97" s="6" t="inlineStr"/>
+      <c r="C97" s="8" t="inlineStr"/>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Silla</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>siiya</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr"/>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 136</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -6660,31 +7352,47 @@
       <c r="C98" s="3" t="inlineStr"/>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Silla</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr"/>
+          <t>Tijera</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>chuptiam</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 09.240</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Tijera</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr"/>
-      <c r="F99" s="6" t="inlineStr"/>
-      <c r="G99" s="6" t="inlineStr"/>
+      <c r="C99" s="8" t="inlineStr"/>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Metate</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>mata</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr"/>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 106</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -6698,31 +7406,47 @@
       <c r="C100" s="3" t="inlineStr"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Metate</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr"/>
+          <t>Bule</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>bule</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 53</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="48" customHeight="1">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Bule</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr"/>
-      <c r="F101" s="6" t="inlineStr"/>
-      <c r="G101" s="6" t="inlineStr"/>
+      <c r="C101" s="8" t="inlineStr"/>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Petate</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>ji'ipte</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr"/>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 76</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="48" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -6733,38 +7457,54 @@
           <t>Objetos y hogar</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr"/>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Petate</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr"/>
+          <t>Fogata</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>taji</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 142</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="48" customHeight="1">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Objetos y hogar</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Fogata</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr"/>
-      <c r="F103" s="6" t="inlineStr"/>
-      <c r="G103" s="6" t="inlineStr"/>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Partes del cuerpo</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Boca</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>teeni</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr"/>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="48" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -6778,31 +7518,47 @@
       <c r="C104" s="3" t="inlineStr"/>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Boca</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr"/>
+          <t>Corazón</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>jiapsi</t>
+        </is>
+      </c>
       <c r="F104" s="3" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 77</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="48" customHeight="1">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Corazón</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr"/>
-      <c r="F105" s="6" t="inlineStr"/>
-      <c r="G105" s="6" t="inlineStr"/>
+      <c r="C105" s="8" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Espalda</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>kooba</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 94</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="48" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -6816,31 +7572,47 @@
       <c r="C106" s="3" t="inlineStr"/>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Espalda</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr"/>
+          <t>Lengua</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>nini</t>
+        </is>
+      </c>
       <c r="F106" s="3" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 116</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="48" customHeight="1">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr"/>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Lengua</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr"/>
-      <c r="F107" s="6" t="inlineStr"/>
-      <c r="G107" s="6" t="inlineStr"/>
+      <c r="C107" s="8" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Mano</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>mamam</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="48" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -6854,31 +7626,47 @@
       <c r="C108" s="3" t="inlineStr"/>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Mano</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr"/>
+          <t>Nariz</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>yeka</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr"/>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 161</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="48" customHeight="1">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Nariz</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr"/>
+      <c r="C109" s="8" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Oído</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>naka</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 113</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="48" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -6892,31 +7680,47 @@
       <c r="C110" s="3" t="inlineStr"/>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Oído</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr"/>
+          <t>Ojos</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>puusim</t>
+        </is>
+      </c>
       <c r="F110" s="3" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 126</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="48" customHeight="1">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr"/>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Ojos</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr"/>
-      <c r="F111" s="6" t="inlineStr"/>
-      <c r="G111" s="6" t="inlineStr"/>
+      <c r="C111" s="8" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Pie</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>woki</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr"/>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 159</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -6930,31 +7734,47 @@
       <c r="C112" s="3" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Pie</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr"/>
+          <t>Sangre</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>oji</t>
+        </is>
+      </c>
       <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 120</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="48" customHeight="1">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Sangre</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr"/>
-      <c r="F113" s="6" t="inlineStr"/>
-      <c r="G113" s="6" t="inlineStr"/>
+      <c r="C113" s="8" t="inlineStr"/>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Cabeza</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>koba</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr"/>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 94</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="48" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -6965,42 +7785,50 @@
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+      <c r="C114" s="3" t="inlineStr"/>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Cabeza</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr"/>
+          <t>Dientes</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>tamim</t>
+        </is>
+      </c>
       <c r="F114" s="3" t="inlineStr"/>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 143</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="48" customHeight="1">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="7" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Dientes</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr"/>
-      <c r="F115" s="6" t="inlineStr"/>
-      <c r="G115" s="6" t="inlineStr"/>
+      <c r="C115" s="8" t="inlineStr"/>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Brazo</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>mamam</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="48" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -7011,42 +7839,50 @@
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+      <c r="C116" s="3" t="inlineStr"/>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Brazo</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr"/>
+          <t>Pierna</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>woki</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr"/>
-      <c r="G116" s="3" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 159</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="48" customHeight="1">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Pierna</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="6" t="inlineStr"/>
-      <c r="G117" s="6" t="inlineStr"/>
+      <c r="C117" s="8" t="inlineStr"/>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Codo</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>moka</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 108</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="48" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -7057,42 +7893,50 @@
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+      <c r="C118" s="3" t="inlineStr"/>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Codo</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr"/>
+          <t>Mejillas</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>japem</t>
+        </is>
+      </c>
       <c r="F118" s="3" t="inlineStr"/>
-      <c r="G118" s="3" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 04.208</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="48" customHeight="1">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Mejillas</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr"/>
-      <c r="F119" s="6" t="inlineStr"/>
-      <c r="G119" s="6" t="inlineStr"/>
+      <c r="C119" s="8" t="inlineStr"/>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Panza</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>toma</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr"/>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 148</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="48" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -7103,42 +7947,50 @@
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+      <c r="C120" s="3" t="inlineStr"/>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Panza</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr"/>
+          <t>Ombligo</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>siiko</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="inlineStr"/>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 136</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="48" customHeight="1">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>Partes del cuerpo</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Ombligo</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr"/>
-      <c r="F121" s="6" t="inlineStr"/>
-      <c r="G121" s="6" t="inlineStr"/>
+      <c r="C121" s="8" t="inlineStr"/>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Dedos</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>mamam</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="48" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -7146,41 +7998,53 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Partes del cuerpo</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+          <t>Adjetivos y estados</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr"/>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Dedos</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr"/>
+          <t>Alegre</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>yantiachi</t>
+        </is>
+      </c>
       <c r="F122" s="3" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 160</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="48" customHeight="1">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="7" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Alegre</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr"/>
-      <c r="F123" s="6" t="inlineStr"/>
-      <c r="G123" s="6" t="inlineStr"/>
+      <c r="C123" s="8" t="inlineStr"/>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>teebe</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr"/>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="48" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -7194,31 +8058,47 @@
       <c r="C124" s="3" t="inlineStr"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr"/>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>saawali</t>
+        </is>
+      </c>
       <c r="F124" s="3" t="inlineStr"/>
-      <c r="G124" s="3" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 131</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="6" t="inlineStr"/>
-      <c r="G125" s="6" t="inlineStr"/>
+      <c r="C125" s="8" t="inlineStr"/>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>tebeo</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr"/>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="48" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -7232,31 +8112,47 @@
       <c r="C126" s="3" t="inlineStr"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Azul</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr"/>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>tosali</t>
+        </is>
+      </c>
       <c r="F126" s="3" t="inlineStr"/>
-      <c r="G126" s="3" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 150</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="48" customHeight="1">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Blanco</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr"/>
+      <c r="C127" s="8" t="inlineStr"/>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Bonito</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>ujyoli</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr"/>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 153</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="48" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -7270,31 +8166,47 @@
       <c r="C128" s="3" t="inlineStr"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Bonito</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr"/>
+          <t>Caliente</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>tatta</t>
+        </is>
+      </c>
       <c r="F128" s="3" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Caliente</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr"/>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr"/>
+      <c r="C129" s="8" t="inlineStr"/>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Caro</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>beje'e</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr"/>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 48</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="48" customHeight="1">
       <c r="A130" s="2" t="n">
@@ -7308,31 +8220,47 @@
       <c r="C130" s="3" t="inlineStr"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Caro</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr"/>
+          <t>Chaparro</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>komcheba</t>
+        </is>
+      </c>
       <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 96</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="48" customHeight="1">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr"/>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Chaparro</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr"/>
+      <c r="C131" s="8" t="inlineStr"/>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Feo</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>ka ujyoli</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr"/>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 87</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="48" customHeight="1">
       <c r="A132" s="2" t="n">
@@ -7346,31 +8274,47 @@
       <c r="C132" s="3" t="inlineStr"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Feo</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr"/>
+          <t>Frío</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>sebe</t>
+        </is>
+      </c>
       <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 132</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr"/>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Frío</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr"/>
-      <c r="F133" s="6" t="inlineStr"/>
-      <c r="G133" s="6" t="inlineStr"/>
+      <c r="C133" s="8" t="inlineStr"/>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Gordo</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>awiri</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr"/>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 41</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="48" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -7384,31 +8328,47 @@
       <c r="C134" s="3" t="inlineStr"/>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Gordo</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr"/>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>chukui</t>
+        </is>
+      </c>
       <c r="F134" s="3" t="inlineStr"/>
-      <c r="G134" s="3" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 62</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="48" customHeight="1">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr"/>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Morado</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr"/>
-      <c r="F135" s="6" t="inlineStr"/>
-      <c r="G135" s="6" t="inlineStr"/>
+      <c r="C135" s="8" t="inlineStr"/>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>sikili</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr"/>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 136</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -7422,31 +8382,47 @@
       <c r="C136" s="3" t="inlineStr"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Negro</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr"/>
+          <t>Triste</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>rojikte</t>
+        </is>
+      </c>
       <c r="F136" s="3" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 129</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="48" customHeight="1">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr"/>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr"/>
-      <c r="F137" s="6" t="inlineStr"/>
-      <c r="G137" s="6" t="inlineStr"/>
+      <c r="C137" s="8" t="inlineStr"/>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>siari</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr"/>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 135</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="48" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -7460,31 +8436,51 @@
       <c r="C138" s="3" t="inlineStr"/>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Triste</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr"/>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>kapee</t>
+        </is>
+      </c>
       <c r="F138" s="3" t="inlineStr"/>
-      <c r="G138" s="3" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 90</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="48" customHeight="1">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr"/>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr"/>
-      <c r="F139" s="6" t="inlineStr"/>
-      <c r="G139" s="6" t="inlineStr"/>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>Cansado</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>lottila</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr"/>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 102</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="48" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -7495,38 +8491,54 @@
           <t>Adjetivos y estados</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr"/>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Café</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr"/>
+          <t>Sediento</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>ba'a muuke</t>
+        </is>
+      </c>
       <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 42</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="48" customHeight="1">
-      <c r="A141" s="5" t="n">
+      <c r="A141" s="7" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>Adjetivos y estados</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>Cansado</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr"/>
-      <c r="F141" s="6" t="inlineStr"/>
-      <c r="G141" s="6" t="inlineStr"/>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Verbos</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr"/>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>Abrir</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>etapo</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr"/>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 66</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="48" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -7534,41 +8546,53 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Adjetivos y estados</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+          <t>Verbos</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr"/>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Sediento</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr"/>
+          <t>Cocinar</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>baake</t>
+        </is>
+      </c>
       <c r="F142" s="3" t="inlineStr"/>
-      <c r="G142" s="3" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 43</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="48" customHeight="1">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr"/>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Abrir</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr"/>
-      <c r="F143" s="6" t="inlineStr"/>
-      <c r="G143" s="6" t="inlineStr"/>
+      <c r="C143" s="8" t="inlineStr"/>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>Comer</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>bwa'e</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr"/>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 54</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="48" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -7582,31 +8606,47 @@
       <c r="C144" s="3" t="inlineStr"/>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Cocinar</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr"/>
+          <t>Comerciar</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>jinu</t>
+        </is>
+      </c>
       <c r="F144" s="3" t="inlineStr"/>
-      <c r="G144" s="3" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 79</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="48" customHeight="1">
-      <c r="A145" s="5" t="n">
+      <c r="A145" s="7" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr"/>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>Comer</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr"/>
-      <c r="F145" s="6" t="inlineStr"/>
-      <c r="G145" s="6" t="inlineStr"/>
+      <c r="C145" s="8" t="inlineStr"/>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>koche</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr"/>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 95</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -7620,31 +8660,47 @@
       <c r="C146" s="3" t="inlineStr"/>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Comerciar</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr"/>
+          <t>Escribir</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>ji'ojte</t>
+        </is>
+      </c>
       <c r="F146" s="3" t="inlineStr"/>
-      <c r="G146" s="3" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 76</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="48" customHeight="1">
-      <c r="A147" s="5" t="n">
+      <c r="A147" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr"/>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>Dormir</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr"/>
-      <c r="F147" s="6" t="inlineStr"/>
-      <c r="G147" s="6" t="inlineStr"/>
+      <c r="C147" s="8" t="inlineStr"/>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>Habitar</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>jiapsa</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr"/>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 77</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -7658,31 +8714,47 @@
       <c r="C148" s="3" t="inlineStr"/>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Escribir</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr"/>
+          <t>Hablar</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>etejo</t>
+        </is>
+      </c>
       <c r="F148" s="3" t="inlineStr"/>
-      <c r="G148" s="3" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 66</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="48" customHeight="1">
-      <c r="A149" s="5" t="n">
+      <c r="A149" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr"/>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Habitar</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr"/>
-      <c r="F149" s="6" t="inlineStr"/>
-      <c r="G149" s="6" t="inlineStr"/>
+      <c r="C149" s="8" t="inlineStr"/>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>Oír</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>jikkaja</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr"/>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 79</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="48" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -7696,31 +8768,47 @@
       <c r="C150" s="3" t="inlineStr"/>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Hablar</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr"/>
+          <t>Trabajar</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>tekipanoa</t>
+        </is>
+      </c>
       <c r="F150" s="3" t="inlineStr"/>
-      <c r="G150" s="3" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 145</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="48" customHeight="1">
-      <c r="A151" s="5" t="n">
+      <c r="A151" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr"/>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>Oír</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr"/>
-      <c r="F151" s="6" t="inlineStr"/>
-      <c r="G151" s="6" t="inlineStr"/>
+      <c r="C151" s="8" t="inlineStr"/>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>bicha</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr"/>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 50</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="48" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -7731,34 +8819,58 @@
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr"/>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Trabajar</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr"/>
+          <t>Correr</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>buite</t>
+        </is>
+      </c>
       <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 53</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="48" customHeight="1">
-      <c r="A153" s="5" t="n">
+      <c r="A153" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr"/>
-      <c r="D153" s="7" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="6" t="inlineStr"/>
-      <c r="G153" s="6" t="inlineStr"/>
+      <c r="C153" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>Bailar</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>ye'e</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="inlineStr"/>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 160</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="48" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -7769,42 +8881,58 @@
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C154" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Correr</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr"/>
+          <t>Cantar</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>bwiika</t>
+        </is>
+      </c>
       <c r="F154" s="3" t="inlineStr"/>
-      <c r="G154" s="3" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 56</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="48" customHeight="1">
-      <c r="A155" s="5" t="n">
+      <c r="A155" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C155" s="8" t="inlineStr">
+      <c r="C155" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>Bailar</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr"/>
-      <c r="F155" s="6" t="inlineStr"/>
-      <c r="G155" s="6" t="inlineStr"/>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>Beber</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>je'e</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr"/>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 75</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="48" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -7815,42 +8943,58 @@
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="C156" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Cantar</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr"/>
+          <t>Reír</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>aache</t>
+        </is>
+      </c>
       <c r="F156" s="3" t="inlineStr"/>
-      <c r="G156" s="3" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 35</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="48" customHeight="1">
-      <c r="A157" s="5" t="n">
+      <c r="A157" s="7" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="B157" s="7" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="C157" s="8" t="inlineStr">
+      <c r="C157" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>Beber</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr"/>
-      <c r="F157" s="6" t="inlineStr"/>
-      <c r="G157" s="6" t="inlineStr"/>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>Buscar</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>jariwa</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr"/>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 75</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="48" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -7858,45 +9002,53 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Verbos</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr"/>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Reír</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr"/>
+          <t>Viejito</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>yo'owe</t>
+        </is>
+      </c>
       <c r="F158" s="3" t="inlineStr"/>
-      <c r="G158" s="3" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 163</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="48" customHeight="1">
-      <c r="A159" s="5" t="n">
+      <c r="A159" s="7" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>Verbos</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>Buscar</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr"/>
-      <c r="F159" s="6" t="inlineStr"/>
-      <c r="G159" s="6" t="inlineStr"/>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr"/>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>Bebé</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>ili uusi</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr"/>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 69</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="48" customHeight="1">
       <c r="A160" s="2" t="n">
@@ -7910,31 +9062,47 @@
       <c r="C160" s="3" t="inlineStr"/>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Viejito</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr"/>
+          <t>Doctor</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>yoi jitebi</t>
+        </is>
+      </c>
       <c r="F160" s="3" t="inlineStr"/>
-      <c r="G160" s="3" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 162</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="48" customHeight="1">
-      <c r="A161" s="5" t="n">
+      <c r="A161" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="5" t="inlineStr">
+      <c r="B161" s="7" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr"/>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>Bebé</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="6" t="inlineStr"/>
-      <c r="G161" s="6" t="inlineStr"/>
+      <c r="C161" s="8" t="inlineStr"/>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>o'ou</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr"/>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 119</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="2" t="n">
@@ -7948,31 +9116,47 @@
       <c r="C162" s="3" t="inlineStr"/>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Doctor</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr"/>
+          <t>Maestro</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>maejto</t>
+        </is>
+      </c>
       <c r="F162" s="3" t="inlineStr"/>
-      <c r="G162" s="3" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 104</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="48" customHeight="1">
-      <c r="A163" s="5" t="n">
+      <c r="A163" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr"/>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>Hombre</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr"/>
-      <c r="F163" s="6" t="inlineStr"/>
-      <c r="G163" s="6" t="inlineStr"/>
+      <c r="C163" s="8" t="inlineStr"/>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>jamut</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr"/>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 74</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="2" t="n">
@@ -7986,31 +9170,47 @@
       <c r="C164" s="3" t="inlineStr"/>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Maestro</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr"/>
+          <t>Músico</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>jiponreo</t>
+        </is>
+      </c>
       <c r="F164" s="3" t="inlineStr"/>
-      <c r="G164" s="3" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 80</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="48" customHeight="1">
-      <c r="A165" s="5" t="n">
+      <c r="A165" s="7" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="5" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr"/>
-      <c r="D165" s="7" t="inlineStr">
-        <is>
-          <t>Mujer</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr"/>
-      <c r="F165" s="6" t="inlineStr"/>
-      <c r="G165" s="6" t="inlineStr"/>
+      <c r="C165" s="8" t="inlineStr"/>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>ili jamut</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr"/>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 69</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="2" t="n">
@@ -8024,31 +9224,47 @@
       <c r="C166" s="3" t="inlineStr"/>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Músico</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr"/>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>uusi</t>
+        </is>
+      </c>
       <c r="F166" s="3" t="inlineStr"/>
-      <c r="G166" s="3" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 154</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="48" customHeight="1">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="7" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr"/>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr"/>
-      <c r="F167" s="6" t="inlineStr"/>
-      <c r="G167" s="6" t="inlineStr"/>
+      <c r="C167" s="8" t="inlineStr"/>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>Vecino</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>kanila jo'akame</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr"/>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 19.540</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="2" t="n">
@@ -8062,31 +9278,51 @@
       <c r="C168" s="3" t="inlineStr"/>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr"/>
+          <t>Viejita</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>asu</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr"/>
-      <c r="G168" s="3" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 40</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="48" customHeight="1">
-      <c r="A169" s="5" t="n">
+      <c r="A169" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="B169" s="7" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr"/>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Vecino</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr"/>
-      <c r="F169" s="6" t="inlineStr"/>
-      <c r="G169" s="6" t="inlineStr"/>
+      <c r="C169" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>Danzante</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>matachiini</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr"/>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 106</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="2" t="n">
@@ -8097,38 +9333,54 @@
           <t>Personas</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr"/>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Viejita</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr"/>
+          <t>Cazador</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>a'amureo</t>
+        </is>
+      </c>
       <c r="F170" s="3" t="inlineStr"/>
-      <c r="G170" s="3" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 20.610</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="48" customHeight="1">
-      <c r="A171" s="5" t="n">
+      <c r="A171" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>Personas</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Danzante</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr"/>
-      <c r="F171" s="6" t="inlineStr"/>
-      <c r="G171" s="6" t="inlineStr"/>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Vestimenta y tradición</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr"/>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>Aretes</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>reepam</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr"/>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 128</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="2" t="n">
@@ -8136,41 +9388,53 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Personas</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+          <t>Vestimenta y tradición</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr"/>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Cazador</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr"/>
+          <t>Bandana</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>buuam</t>
+        </is>
+      </c>
       <c r="F172" s="3" t="inlineStr"/>
-      <c r="G172" s="3" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 53</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="48" customHeight="1">
-      <c r="A173" s="5" t="n">
+      <c r="A173" s="7" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr"/>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>Aretes</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr"/>
-      <c r="F173" s="6" t="inlineStr"/>
-      <c r="G173" s="6" t="inlineStr"/>
+      <c r="C173" s="8" t="inlineStr"/>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>Blusa</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>supem</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr"/>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 139</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="2" t="n">
@@ -8184,31 +9448,47 @@
       <c r="C174" s="3" t="inlineStr"/>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Bandana</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr"/>
+          <t>Camisa</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>supem</t>
+        </is>
+      </c>
       <c r="F174" s="3" t="inlineStr"/>
-      <c r="G174" s="3" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 139</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="48" customHeight="1">
-      <c r="A175" s="5" t="n">
+      <c r="A175" s="7" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="B175" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr"/>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>Blusa</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr"/>
-      <c r="F175" s="6" t="inlineStr"/>
-      <c r="G175" s="6" t="inlineStr"/>
+      <c r="C175" s="8" t="inlineStr"/>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>Collar</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>kooka</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr"/>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 96</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="2" t="n">
@@ -8222,31 +9502,47 @@
       <c r="C176" s="3" t="inlineStr"/>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Camisa</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr"/>
+          <t>Faja</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>wikosa</t>
+        </is>
+      </c>
       <c r="F176" s="3" t="inlineStr"/>
-      <c r="G176" s="3" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 06.570</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="48" customHeight="1">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="7" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="B177" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr"/>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>Collar</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr"/>
-      <c r="F177" s="6" t="inlineStr"/>
-      <c r="G177" s="6" t="inlineStr"/>
+      <c r="C177" s="8" t="inlineStr"/>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>Falda</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>ko'arim</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr"/>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 93</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="2" t="n">
@@ -8260,31 +9556,47 @@
       <c r="C178" s="3" t="inlineStr"/>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Faja</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr"/>
+          <t>Huarache</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>beabocham</t>
+        </is>
+      </c>
       <c r="F178" s="3" t="inlineStr"/>
-      <c r="G178" s="3" t="inlineStr"/>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 47</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="48" customHeight="1">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr"/>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Falda</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr"/>
-      <c r="F179" s="6" t="inlineStr"/>
-      <c r="G179" s="6" t="inlineStr"/>
+      <c r="C179" s="8" t="inlineStr"/>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>Pantalones</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>saaweam</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr"/>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 131</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="2" t="n">
@@ -8298,31 +9610,51 @@
       <c r="C180" s="3" t="inlineStr"/>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Huarache</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr"/>
+          <t>Sombrero</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>mo'obei</t>
+        </is>
+      </c>
       <c r="F180" s="3" t="inlineStr"/>
-      <c r="G180" s="3" t="inlineStr"/>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 108</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="48" customHeight="1">
-      <c r="A181" s="5" t="n">
+      <c r="A181" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr"/>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>Pantalones</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr"/>
-      <c r="F181" s="6" t="inlineStr"/>
-      <c r="G181" s="6" t="inlineStr"/>
+      <c r="C181" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>Ténabaris</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>teneboim</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr"/>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 146</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="2" t="n">
@@ -8333,34 +9665,58 @@
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr"/>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Sombrero</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr"/>
+          <t>Máscara</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>majkaa</t>
+        </is>
+      </c>
       <c r="F182" s="3" t="inlineStr"/>
-      <c r="G182" s="3" t="inlineStr"/>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 104</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="48" customHeight="1">
-      <c r="A183" s="5" t="n">
+      <c r="A183" s="7" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="B183" s="7" t="inlineStr">
         <is>
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr"/>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>Taparrabo</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr"/>
-      <c r="F183" s="6" t="inlineStr"/>
-      <c r="G183" s="6" t="inlineStr"/>
+      <c r="C183" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>Tambor</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>kubaji</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr"/>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 97</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="2" t="n">
@@ -8371,42 +9727,58 @@
           <t>Vestimenta y tradición</t>
         </is>
       </c>
-      <c r="C184" s="9" t="inlineStr">
+      <c r="C184" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Ténabaris</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr"/>
+          <t>Sonaja</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>ayam</t>
+        </is>
+      </c>
       <c r="F184" s="3" t="inlineStr"/>
-      <c r="G184" s="3" t="inlineStr"/>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 41</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="48" customHeight="1">
-      <c r="A185" s="5" t="n">
+      <c r="A185" s="7" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="5" t="inlineStr">
-        <is>
-          <t>Vestimenta y tradición</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr">
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Números</t>
+        </is>
+      </c>
+      <c r="C185" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
-        <is>
-          <t>Máscara</t>
-        </is>
-      </c>
-      <c r="E185" s="6" t="inlineStr"/>
-      <c r="F185" s="6" t="inlineStr"/>
-      <c r="G185" s="6" t="inlineStr"/>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>Uno</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>seenu</t>
+        </is>
+      </c>
+      <c r="F185" s="8" t="inlineStr"/>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 133</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="2" t="n">
@@ -8414,45 +9786,61 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Vestimenta y tradición</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
+          <t>Números</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Tambor</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr"/>
+          <t>Dos</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>woi</t>
+        </is>
+      </c>
       <c r="F186" s="3" t="inlineStr"/>
-      <c r="G186" s="3" t="inlineStr"/>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 68</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="48" customHeight="1">
-      <c r="A187" s="5" t="n">
+      <c r="A187" s="7" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>Vestimenta y tradición</t>
-        </is>
-      </c>
-      <c r="C187" s="8" t="inlineStr">
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>Números</t>
+        </is>
+      </c>
+      <c r="C187" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>Sonaja</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr"/>
-      <c r="F187" s="6" t="inlineStr"/>
-      <c r="G187" s="6" t="inlineStr"/>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>Tres</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>baji</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr"/>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 44</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="2" t="n">
@@ -8463,42 +9851,58 @@
           <t>Números</t>
         </is>
       </c>
-      <c r="C188" s="9" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Uno</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr"/>
+          <t>Cuatro</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>naiki</t>
+        </is>
+      </c>
       <c r="F188" s="3" t="inlineStr"/>
-      <c r="G188" s="3" t="inlineStr"/>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 113</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="48" customHeight="1">
-      <c r="A189" s="5" t="n">
+      <c r="A189" s="7" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t>Números</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr">
+      <c r="C189" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>Dos</t>
-        </is>
-      </c>
-      <c r="E189" s="6" t="inlineStr"/>
-      <c r="F189" s="6" t="inlineStr"/>
-      <c r="G189" s="6" t="inlineStr"/>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>mamni</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr"/>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 105</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="2" t="n">
@@ -8509,42 +9913,58 @@
           <t>Números</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr">
+      <c r="C190" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Tres</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr"/>
+          <t>Seis</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>busani</t>
+        </is>
+      </c>
       <c r="F190" s="3" t="inlineStr"/>
-      <c r="G190" s="3" t="inlineStr"/>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 53</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="48" customHeight="1">
-      <c r="A191" s="5" t="n">
+      <c r="A191" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>Números</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
+      <c r="C191" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>Cuatro</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr"/>
-      <c r="F191" s="6" t="inlineStr"/>
-      <c r="G191" s="6" t="inlineStr"/>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>goo busani</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr"/>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 68</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="2" t="n">
@@ -8555,42 +9975,58 @@
           <t>Números</t>
         </is>
       </c>
-      <c r="C192" s="9" t="inlineStr">
+      <c r="C192" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Cinco</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr"/>
+          <t>Ocho</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>gonaiki</t>
+        </is>
+      </c>
       <c r="F192" s="3" t="inlineStr"/>
-      <c r="G192" s="3" t="inlineStr"/>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 68</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="48" customHeight="1">
-      <c r="A193" s="5" t="n">
+      <c r="A193" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="B193" s="7" t="inlineStr">
         <is>
           <t>Números</t>
         </is>
       </c>
-      <c r="C193" s="8" t="inlineStr">
+      <c r="C193" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D193" s="7" t="inlineStr">
-        <is>
-          <t>Seis</t>
-        </is>
-      </c>
-      <c r="E193" s="6" t="inlineStr"/>
-      <c r="F193" s="6" t="inlineStr"/>
-      <c r="G193" s="6" t="inlineStr"/>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>Nueve</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>batani</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr"/>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 46</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="48" customHeight="1">
       <c r="A194" s="2" t="n">
@@ -8601,42 +10037,54 @@
           <t>Números</t>
         </is>
       </c>
-      <c r="C194" s="9" t="inlineStr">
+      <c r="C194" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Siete</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr"/>
+          <t>Diez</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>goj mamni</t>
+        </is>
+      </c>
       <c r="F194" s="3" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 67</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="48" customHeight="1">
-      <c r="A195" s="5" t="n">
+      <c r="A195" s="7" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="5" t="inlineStr">
-        <is>
-          <t>Números</t>
-        </is>
-      </c>
-      <c r="C195" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D195" s="7" t="inlineStr">
-        <is>
-          <t>Ocho</t>
-        </is>
-      </c>
-      <c r="E195" s="6" t="inlineStr"/>
-      <c r="F195" s="6" t="inlineStr"/>
-      <c r="G195" s="6" t="inlineStr"/>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>Lugares</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr"/>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>jo'ara</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr"/>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 82</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="48" customHeight="1">
       <c r="A196" s="2" t="n">
@@ -8644,45 +10092,53 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Números</t>
-        </is>
-      </c>
-      <c r="C196" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
+          <t>Lugares</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr"/>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Nueve</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr"/>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>bwe'u jo'ara</t>
+        </is>
+      </c>
       <c r="F196" s="3" t="inlineStr"/>
-      <c r="G196" s="3" t="inlineStr"/>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 19.150</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="48" customHeight="1">
-      <c r="A197" s="5" t="n">
+      <c r="A197" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="5" t="inlineStr">
-        <is>
-          <t>Números</t>
-        </is>
-      </c>
-      <c r="C197" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D197" s="7" t="inlineStr">
-        <is>
-          <t>Diez</t>
-        </is>
-      </c>
-      <c r="E197" s="6" t="inlineStr"/>
-      <c r="F197" s="6" t="inlineStr"/>
-      <c r="G197" s="6" t="inlineStr"/>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>Lugares</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr"/>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>Escuela</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="inlineStr">
+        <is>
+          <t>ejkuela</t>
+        </is>
+      </c>
+      <c r="F197" s="8" t="inlineStr"/>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 64</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="48" customHeight="1">
       <c r="A198" s="2" t="n">
@@ -8696,31 +10152,47 @@
       <c r="C198" s="3" t="inlineStr"/>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr"/>
+          <t>Huerta</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>echia</t>
+        </is>
+      </c>
       <c r="F198" s="3" t="inlineStr"/>
-      <c r="G198" s="3" t="inlineStr"/>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 64</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="48" customHeight="1">
-      <c r="A199" s="5" t="n">
+      <c r="A199" s="7" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="5" t="inlineStr">
+      <c r="B199" s="7" t="inlineStr">
         <is>
           <t>Lugares</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr"/>
-      <c r="D199" s="7" t="inlineStr">
-        <is>
-          <t>Cementerio</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr"/>
-      <c r="F199" s="6" t="inlineStr"/>
-      <c r="G199" s="6" t="inlineStr"/>
+      <c r="C199" s="8" t="inlineStr"/>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>Iglesia</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="inlineStr">
+        <is>
+          <t>te'opo</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr"/>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 144</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="48" customHeight="1">
       <c r="A200" s="2" t="n">
@@ -8734,31 +10206,47 @@
       <c r="C200" s="3" t="inlineStr"/>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Ciudad</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr"/>
+          <t>Pueblo</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>pueplo</t>
+        </is>
+      </c>
       <c r="F200" s="3" t="inlineStr"/>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 126</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="48" customHeight="1">
-      <c r="A201" s="5" t="n">
+      <c r="A201" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t>Lugares</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr"/>
-      <c r="D201" s="7" t="inlineStr">
-        <is>
-          <t>Escuela</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr"/>
-      <c r="F201" s="6" t="inlineStr"/>
-      <c r="G201" s="6" t="inlineStr"/>
+      <c r="C201" s="8" t="inlineStr"/>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="E201" s="10" t="inlineStr">
+        <is>
+          <t>tienra</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr"/>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>IDS Yaqui 11.860</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="48" customHeight="1">
       <c r="A202" s="2" t="n">
@@ -8766,37 +10254,61 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Lugares</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr"/>
+          <t>Tiempo</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Huerta</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr"/>
+          <t>Mañana</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>matchu</t>
+        </is>
+      </c>
       <c r="F202" s="3" t="inlineStr"/>
-      <c r="G202" s="3" t="inlineStr"/>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 106</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="48" customHeight="1">
-      <c r="A203" s="5" t="n">
+      <c r="A203" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="5" t="inlineStr">
-        <is>
-          <t>Lugares</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr"/>
-      <c r="D203" s="7" t="inlineStr">
-        <is>
-          <t>Iglesia</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr"/>
-      <c r="F203" s="6" t="inlineStr"/>
-      <c r="G203" s="6" t="inlineStr"/>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Tiempo</t>
+        </is>
+      </c>
+      <c r="C203" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="inlineStr">
+        <is>
+          <t>kupsa'ite</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr"/>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 98</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="48" customHeight="1">
       <c r="A204" s="2" t="n">
@@ -8804,37 +10316,57 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Lugares</t>
+          <t>Tiempo</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr"/>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Pueblo</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr"/>
+          <t>Noche</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>tukaa</t>
+        </is>
+      </c>
       <c r="F204" s="3" t="inlineStr"/>
-      <c r="G204" s="3" t="inlineStr"/>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 151</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="48" customHeight="1">
-      <c r="A205" s="5" t="n">
+      <c r="A205" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="5" t="inlineStr">
-        <is>
-          <t>Lugares</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr"/>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>Tienda</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr"/>
-      <c r="F205" s="6" t="inlineStr"/>
-      <c r="G205" s="6" t="inlineStr"/>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>Tiempo</t>
+        </is>
+      </c>
+      <c r="C205" s="13" t="inlineStr">
+        <is>
+          <t>[Por ilustrar]</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="inlineStr">
+        <is>
+          <t>taa'a</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr"/>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 141</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="48" customHeight="1">
       <c r="A206" s="2" t="n">
@@ -8845,133 +10377,61 @@
           <t>Tiempo</t>
         </is>
       </c>
-      <c r="C206" s="9" t="inlineStr">
+      <c r="C206" s="12" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Mañana</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr"/>
+          <t>Hoy</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>ían</t>
+        </is>
+      </c>
       <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="3" t="inlineStr"/>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Diccionario p. 69</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="48" customHeight="1">
-      <c r="A207" s="5" t="n">
+      <c r="A207" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="B207" s="7" t="inlineStr">
         <is>
           <t>Tiempo</t>
         </is>
       </c>
-      <c r="C207" s="8" t="inlineStr">
+      <c r="C207" s="13" t="inlineStr">
         <is>
           <t>[Por ilustrar]</t>
         </is>
       </c>
-      <c r="D207" s="7" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr"/>
-      <c r="F207" s="6" t="inlineStr"/>
-      <c r="G207" s="6" t="inlineStr"/>
-    </row>
-    <row r="208" ht="48" customHeight="1">
-      <c r="A208" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>Tiempo</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr"/>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>Noche</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr"/>
-      <c r="F208" s="3" t="inlineStr"/>
-      <c r="G208" s="3" t="inlineStr"/>
-    </row>
-    <row r="209" ht="48" customHeight="1">
-      <c r="A209" s="5" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
-        <is>
-          <t>Tiempo</t>
-        </is>
-      </c>
-      <c r="C209" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D209" s="7" t="inlineStr">
-        <is>
-          <t>Día</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr"/>
-      <c r="F209" s="6" t="inlineStr"/>
-      <c r="G209" s="6" t="inlineStr"/>
-    </row>
-    <row r="210" ht="48" customHeight="1">
-      <c r="A210" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>Tiempo</t>
-        </is>
-      </c>
-      <c r="C210" s="9" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>Hoy</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr"/>
-      <c r="F210" s="3" t="inlineStr"/>
-      <c r="G210" s="3" t="inlineStr"/>
-    </row>
-    <row r="211" ht="48" customHeight="1">
-      <c r="A211" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
-        <is>
-          <t>Tiempo</t>
-        </is>
-      </c>
-      <c r="C211" s="8" t="inlineStr">
-        <is>
-          <t>[Por ilustrar]</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
+      <c r="D207" s="9" t="inlineStr">
         <is>
           <t>Ayer</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr"/>
-      <c r="F211" s="6" t="inlineStr"/>
-      <c r="G211" s="6" t="inlineStr"/>
+      <c r="E207" s="10" t="inlineStr">
+        <is>
+          <t>tuuka</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="inlineStr"/>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>Diccionario p. 151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G211"/>
+  <autoFilter ref="A1:G207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
